--- a/API文本价格.xlsx
+++ b/API文本价格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="文本模型价格" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="已彻底下线（调用会报错）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="数据来源与口径" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文本模型价格'!$A$2:$I$65</definedName>
@@ -675,7 +675,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-07-28</t>
+          <t>TEXT 文本模型 API 价格（USD / 每 1M tokens，标准同步档）｜自动更新于 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>$2.50</t>
+          <t>$2.00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>$0.25</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>$1.00</t>
+          <t>$0.20</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$0.10</t>
+          <t>$0.02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>$6.00</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1.05M</t>
+          <t>272K</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="1">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>自动更新于 2026-07-28｜主数据源：LiteLLM model_prices_and_context_window.json</t>
+          <t>自动更新于 2026-08-03｜主数据源：LiteLLM model_prices_and_context_window.json</t>
         </is>
       </c>
     </row>
